--- a/migracion/Propuesta_2026-07.xlsx
+++ b/migracion/Propuesta_2026-07.xlsx
@@ -440,12 +440,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
@@ -532,46 +532,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Julio Colombia 2026.xlsx (EF Colombia.zip)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Balance cuadra</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>AVISO</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>activo 6106667431.61 vs pasivo+patrimonio 12284992538.30 (dif -6178325106.69)</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Partida doble</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>debitos 2946132966.26 = creditos 2946132966.26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Julio 2026 USA.xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
+          <t>Julio Colombia 2026.xlsx (EF Colombia.zip)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Abre como Excel</t>
+          <t>El arbol suma igual en cada nivel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75 cuentas leidas</t>
+          <t>clase, grupo, cuenta y subcuenta dan lo mismo</t>
         </is>
       </c>
     </row>
@@ -598,61 +598,61 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Abre como Excel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>75 cuentas leidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Julio 2026 USA.xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Continuidad de saldos</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>el saldo inicial es el final del mes anterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>EE.UU.</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Julio 2026 USA.xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Balance cuadra</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>AVISO</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>activo 928705.32 vs pasivo+patrimonio 977253.25 (dif -48547.93)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Julio Peru 2026.xlsx (EF Peru.zip)</t>
+          <t>Julio 2026 USA.xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Abre como Excel</t>
+          <t>Partida doble</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -662,78 +662,78 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50 cuentas leidas</t>
+          <t>debitos 30391.01 = creditos 30391.01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Julio 2026 USA.xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>El arbol suma igual en cada nivel</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>clase, grupo, cuenta y subcuenta dan lo mismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Perú</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Julio Peru 2026.xlsx (EF Peru.zip)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Continuidad de saldos</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Abre como Excel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>el saldo inicial es el final del mes anterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Perú</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Julio Peru 2026.xlsx (EF Peru.zip)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Balance cuadra</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>AVISO</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>activo 90126.14 vs pasivo+patrimonio 67849.15 (dif 22276.99)</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>50 cuentas leidas</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Costa Rica Julio 2026 .xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
+          <t>Julio Peru 2026.xlsx (EF Peru.zip)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abre como Excel</t>
+          <t>Continuidad de saldos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -743,61 +743,169 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>45 cuentas leidas</t>
+          <t>el saldo inicial es el final del mes anterior</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Julio Peru 2026.xlsx (EF Peru.zip)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Partida doble</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>debitos 86362.56 = creditos 86362.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Julio Peru 2026.xlsx (EF Peru.zip)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>El arbol suma igual en cada nivel</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>clase, grupo, cuenta y subcuenta dan lo mismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Costa Rica Julio 2026 .xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Abre como Excel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>45 cuentas leidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Costa Rica Julio 2026 .xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Continuidad de saldos</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>el saldo inicial es el final del mes anterior</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Costa Rica Julio 2026 .xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Balance cuadra</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>AVISO</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>activo 134607.82 vs pasivo+patrimonio 25519.52 (dif 109088.30)</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Partida doble</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>debitos 140140.56 = creditos 140140.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Costa Rica Julio 2026 .xlsx (Fwd_ Estados financieros Mensuales Filiales.zip)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>El arbol suma igual en cada nivel</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>clase, grupo, cuenta y subcuenta dan lo mismo</t>
         </is>
       </c>
     </row>
